--- a/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 0,0</t>
+          <t>-5,89; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,69</t>
+          <t>-2,51; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,99</t>
+          <t>-1,5; 1,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,65</t>
+          <t>-0,93; 2,97</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,61</t>
+          <t>-0,32; 0,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,79</t>
+          <t>-0,32; 0,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,21</t>
+          <t>-0,36; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,41</t>
+          <t>-0,89; 0,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,81</t>
+          <t>-0,23; 0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,44</t>
+          <t>-0,46; 0,41</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,18; —</t>
+          <t>-64,28; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 644,22</t>
+          <t>-62,54; 857,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,31; 427,57</t>
+          <t>-100,0; 486,92</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,28</t>
+          <t>-0,64; 0,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,53</t>
+          <t>-0,5; 0,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,22</t>
+          <t>-0,03; 1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,41</t>
+          <t>-0,49; 0,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,57</t>
+          <t>-0,22; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,35</t>
+          <t>-0,33; 0,33</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,57; 484,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,51; —</t>
+          <t>-41,53; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 383,28</t>
+          <t>-51,82; 332,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,34; 235,97</t>
+          <t>-69,43; 228,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,0</t>
+          <t>-4,99; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,0</t>
+          <t>-2,25; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,65</t>
+          <t>-1,5; 2,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,97</t>
+          <t>-0,95; 2,92</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,74</t>
+          <t>-0,33; 0,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,84</t>
+          <t>-0,32; 0,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,25</t>
+          <t>-0,46; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,38</t>
+          <t>-0,89; 0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,79</t>
+          <t>-0,19; 0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,41</t>
+          <t>-0,46; 0,42</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,28; —</t>
+          <t>-71,03; 1015,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 857,47</t>
+          <t>-55,92; 770,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 486,92</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-1,33; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,79</t>
+          <t>-0,32; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,0</t>
+          <t>-0,91; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,28</t>
+          <t>-0,64; 0,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,5</t>
+          <t>-0,5; 0,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,29</t>
+          <t>-0,07; 1,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,37</t>
+          <t>-0,48; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,61</t>
+          <t>-0,23; 0,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,33</t>
+          <t>-0,33; 0,3</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 484,36</t>
+          <t>-87,51; 541,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,53; —</t>
+          <t>-46,16; 1229,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 332,02</t>
+          <t>-52,76; 325,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,43; 228,45</t>
+          <t>-71,22; 211,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,0</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,03</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,06</t>
+          <t>-5,91; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>-2,47; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,12</t>
+          <t>-1,46; 1,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,92</t>
+          <t>-0,94; 2,65</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>31,18%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,74</t>
+          <t>-0,45; 1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>-0,91; 0,41</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-0,48; 0,61</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>-0,32; 0,79</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 1,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 0,41</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,79</t>
+          <t>-0,23; 0,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,42</t>
+          <t>-0,4; 0,44</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-36,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>88,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>104,82%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>87,56%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-36,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,18; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,03; 1015,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,92; 770,08</t>
+          <t>-57,78; 644,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,31; 427,57</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,0</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,64</t>
+          <t>-0,32; 0,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,0</t>
+          <t>-0,79; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,21</t>
+          <t>-0,11; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,56</t>
+          <t>-0,51; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,2</t>
+          <t>-0,66; 0,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,42</t>
+          <t>-0,5; 0,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,58</t>
+          <t>-0,19; 0,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,3</t>
+          <t>-0,34; 0,35</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>170,83%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-7,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-48,35%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>170,83%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-7,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,51; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 541,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 1229,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 325,9</t>
+          <t>-50,22; 383,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 211,39</t>
+          <t>-71,34; 235,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,285 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.38310888954622</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9233091873765318</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.458327233769463</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.4547447740150203</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.08703949550110972</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.6368120671204498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,01</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,91; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 4,69</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 1,99</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-0,94; 2,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.908035767089616</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.474900460269908</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.461307520826023</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-0.9413145467076078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>85,4%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.007161682866071</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.100874057342708</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.686000393251905</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.986062843523808</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.649415093096188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.3118262921275925</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1167267365112472</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.8540145360217962</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 1,21</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 0,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 0,61</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 0,79</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,23; 0,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,44</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>87,56%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-36,54%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>104,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,31%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.385470715367199</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1608595487597898</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1403608773870384</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1665302962897446</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.2652538891442936</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.007152679386341482</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-70,18; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-57,78; 644,22</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-83,31; 427,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.45244617711153</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.905552305018841</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.4757727790546283</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.3193601469509007</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.2337366286617889</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.3967647614969264</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.206666674560967</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.410361395361582</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6060212272463397</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.7931794449995924</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.8094585246134178</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.4380715506313342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,94</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 0,79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 0,0</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.8755568406295814</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3653758189206566</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.8834676294076729</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.048184713764437</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8579803690016506</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.02313579084190324</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.7017577000309838</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.5777815569454752</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8331239139116786</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>6.442199128298543</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>4.275664293575759</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +886,275 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.3889169538687847</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3007993077296526</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3007993077296526</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.04043837860087666</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.1576107943078884</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,11; 1,22</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,51; 0,41</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 0,28</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 0,53</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,19; 0,57</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 0,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>-1.791454020658499</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.511910075943192</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.3159606744760504</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.794642750299129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>170,83%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-7,73%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-48,35%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-1,89%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.939641015986373</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.7874522300552415</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-50,51; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-50,22; 383,28</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-71,34; 235,97</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.2565711236876417</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.4968966065604405</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.02248449093148479</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.178179918439679</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.01092699250970644</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.1688245547773866</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.006196296664757973</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.1053689196608486</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.5097779688185111</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.6616184579389111</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4951885641191053</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.1906458247257426</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.3424375470604578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.220308516268801</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.4063744777003611</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.2822537183310023</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.532616825420581</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.5739943058823571</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.3452635255497198</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1.708324284247462</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.07730139705135047</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4834837795779799</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.02964993858048971</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.5138206071688227</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.01885854174875365</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.5051482290679074</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.5021583372788507</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.7134117510899395</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>3.832783014884686</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2.359696171150312</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1162,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
